--- a/week-01/EDM_Den_Customer Survey.xlsx
+++ b/week-01/EDM_Den_Customer Survey.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thaniastaana\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5EE98C33-A6A0-4A28-8FBB-A7B7489DE719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC5B4437-4412-4257-88B9-706B7D4A255E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="0" windowWidth="14844" windowHeight="9636" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="EDM Den" sheetId="1" r:id="rId1"/>
     <sheet name="How Often" sheetId="4" r:id="rId2"/>
+    <sheet name="Would You Promote" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="10" r:id="rId3"/>
+    <pivotCache cacheId="19" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -163,6 +164,9 @@
   </si>
   <si>
     <t>Count of How often do you come to EDM Den?</t>
+  </si>
+  <si>
+    <t>Count of Would you like to promote EDM Den for commission?</t>
   </si>
 </sst>
 </file>
@@ -171,7 +175,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -202,18 +206,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="45" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -224,11 +224,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -241,45 +248,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="28" formatCode="mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -307,6 +275,39 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="28" formatCode="mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -730,7 +731,349 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[EDM_Den_Customer Survey.xlsx]Would You Promote!PivotTable5</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Would You Promote'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Would You Promote'!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>No</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Yes</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Would You Promote'!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C1D-4D30-A2B1-683BB6604EE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1241,6 +1584,525 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -1314,6 +2176,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2579370</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>331470</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1854ED6E-02C4-9E7E-E3AF-8443F182A6C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="thania staana" refreshedDate="46313.901395023146" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="5" xr:uid="{5B9C1B2A-3F4F-47EA-91D2-BB34C1E44E45}">
   <cacheSource type="worksheet">
@@ -1329,10 +2232,10 @@
         <n v="5"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Start time" numFmtId="166">
+    <cacheField name="Start time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-10-14T21:11:26" maxDate="2026-10-16T22:55:25"/>
     </cacheField>
-    <cacheField name="Completion time" numFmtId="166">
+    <cacheField name="Completion time" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-10-14T21:12:53" maxDate="2026-10-16T23:00:08"/>
     </cacheField>
     <cacheField name="Time to complete" numFmtId="45">
@@ -1371,7 +2274,10 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Would you like to promote EDM Den for commission?" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="No"/>
+        <s v="Yes"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -1398,7 +2304,7 @@
     <s v="N/A"/>
     <s v="1-2 Hours Before Closing"/>
     <s v="No"/>
-    <s v="No"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -1414,7 +2320,7 @@
     <s v="You are my one and only !"/>
     <s v="Till Closing"/>
     <s v="Yes"/>
-    <s v="Yes"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="2"/>
@@ -1430,7 +2336,7 @@
     <s v="Slate"/>
     <s v="1-2 Hours Before Closing"/>
     <s v="Yes"/>
-    <s v="No"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="3"/>
@@ -1446,7 +2352,7 @@
     <s v="This question is required, even if you select no"/>
     <s v="Earlier"/>
     <s v="Yes"/>
-    <s v="No"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="4"/>
@@ -1462,13 +2368,13 @@
     <s v="N/A"/>
     <s v="1-2 Hours Before Closing"/>
     <s v="Yes"/>
-    <s v="No"/>
+    <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5CAC16A-3BF1-47AA-B542-6C2B63BD09F1}" name="PivotTable2" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5CAC16A-3BF1-47AA-B542-6C2B63BD09F1}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0">
@@ -1481,8 +2387,8 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField numFmtId="45" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -1552,27 +2458,95 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F1287161-CA8C-4EBA-ACDD-DA3E9DE3B845}" name="PivotTable5" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="45" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="13"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Would you like to promote EDM Den for commission?" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:N7" totalsRowCount="1">
   <autoFilter ref="A1:N6" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="17" totalsRowDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="16" totalsRowDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="15" totalsRowDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{DE5568D2-8B1A-4F57-9AAA-0B859556F0EB}" name="Time to complete" totalsRowFunction="custom" dataDxfId="14" totalsRowDxfId="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Completion time" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{DE5568D2-8B1A-4F57-9AAA-0B859556F0EB}" name="Time to complete" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>C2-B2</calculatedColumnFormula>
       <totalsRowFormula>AVERAGE(Table1[Time to complete])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="27" totalsRowDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="26" totalsRowDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="25" totalsRowDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you come to EDM Den?" dataDxfId="24" totalsRowDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What type of EDM genre do you enjoy most?" dataDxfId="23" totalsRowDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Do you go to other clubs?" dataDxfId="22" totalsRowDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="What other clubs do you go to, if yes?" dataDxfId="21" totalsRowDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How late do you stay out in EDM Den?" dataDxfId="20" totalsRowDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Would you recommend people to come to EDM Den?" totalsRowLabel="Because there was 4 &quot;Yes&quot; and 1 &quot;No&quot; to recommend, it is somewhat likely" dataDxfId="19" totalsRowDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Would you like to promote EDM Den for commission?" dataDxfId="18" totalsRowDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Email" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Name" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Last modified time" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="How often do you come to EDM Den?" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="What type of EDM genre do you enjoy most?" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Do you go to other clubs?" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="What other clubs do you go to, if yes?" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="How late do you stay out in EDM Den?" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Would you recommend people to come to EDM Den?" totalsRowLabel="Because there was 4 &quot;Yes&quot; and 1 &quot;No&quot; to recommend, it is somewhat likely" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Would you like to promote EDM Den for commission?" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1879,9 +2853,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20" style="5" customWidth="1"/>
     <col min="5" max="14" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1889,13 +2863,13 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E1" t="s">
@@ -1933,13 +2907,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>46309.882939814815</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="3">
         <v>46309.883946759262</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="5">
         <f t="shared" ref="D2:D6" si="0">C2-B2</f>
         <v>1.006944446999114E-3</v>
       </c>
@@ -1973,13 +2947,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>46310.471643518518</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="3">
         <v>46310.476423611108</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="5">
         <f t="shared" si="0"/>
         <v>4.7800925894989632E-3</v>
       </c>
@@ -2013,13 +2987,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="3">
         <v>46311.562557870369</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="3">
         <v>46311.563877314817</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="5">
         <f t="shared" si="0"/>
         <v>1.3194444472901523E-3</v>
       </c>
@@ -2053,13 +3027,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>46311.693819444445</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="3">
         <v>46311.694618055553</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="5">
         <f t="shared" si="0"/>
         <v>7.9861110862111673E-4</v>
       </c>
@@ -2093,13 +3067,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="3">
         <v>46311.955150462964</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="3">
         <v>46311.958425925928</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <f t="shared" si="0"/>
         <v>3.275462964666076E-3</v>
       </c>
@@ -2130,39 +3104,30 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="7">
+      <c r="C7" s="3"/>
+      <c r="D7" s="5">
         <f>AVERAGE(Table1[Time to complete])</f>
         <v>2.2361111114150845E-3</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="N7" s="3"/>
     </row>
     <row r="8" spans="1:14" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="6"/>
     </row>
     <row r="1048576" spans="4:4" x14ac:dyDescent="0.3">
-      <c r="D1048576" s="7">
+      <c r="D1048576" s="5">
         <f>AVERAGE(D2:D1048575)</f>
         <v>2.2361111114150845E-3</v>
       </c>
@@ -2190,7 +3155,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="7" t="s">
         <v>38</v>
       </c>
       <c r="B3" t="s">
@@ -2198,42 +3163,89 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B801DE46-80CD-45E2-8F57-CDFE2E1E89B1}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="9">
         <v>5</v>
       </c>
     </row>
